--- a/originales/respuestas/2025/01. Calificadas/bucle p35/Subred Integrada De Servicios De Salud Sur Occidente.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p35/Subred Integrada De Servicios De Salud Sur Occidente.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="QeOOB9zhaIXHbKrKSjxmC9ere/+thaNjBxiAehNBZ9g="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ld0XHWe/6w5WMikh8zsVdA2CdWMtzll+aMeCak9jJTY="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
   <si>
     <t>Entidad</t>
   </si>
@@ -79,7 +79,7 @@
  Aplica para todos los colaboradores y para los grupos de interés de la Subred Integrada de Servicios de salud Sur Occidente E.S.E.</t>
   </si>
   <si>
-    <t>https://innovebogota.veeduriadistrital.gov.co:4282/app/api_preguntas/public/api/download-file-by-nombre/208/Acuerdo_087_del_18_de_diciembre_de_2024 (2).pdf</t>
+    <t>https://innovebogota.veeduriadistrital.gov.co:4282/app/api_preguntas/public/api/download-file-by-nombre/208/01-01-PL-0003 Plan estrategico 2025-2028.pdf</t>
   </si>
   <si>
     <t>Jerarquía del instrumento</t>
@@ -110,7 +110,7 @@
  Sin embargo, a partir del avance de la implementación de la Chequera de Salario Emocional y reconociendo la necesidad de contar con recursos internos para el cargue de puntos asociados al uso de los beneficios, se identificó la necesidad de crear un nuevo componente. Por ello, para la vigencia 2025 se incorpora un nuevo eje en el Plan de Bienestar, denominado "Eje de Reconocimiento e Incentivos", el cual busca fortalecer aún más el compromiso, la motivación y la satisfacción de los colaboradores.</t>
   </si>
   <si>
-    <t>https://innovebogota.veeduriadistrital.gov.co:4282/app/api_preguntas/public/api/download-file-by-nombre/208/01-01-PL-0003 Plan estrategico 2025-2028.pdf</t>
+    <t>https://innovebogota.veeduriadistrital.gov.co:4282/app/api_preguntas/public/api/download-file-by-nombre/208/04-03-PL-0001_Plan_de_bienestar_social_e_incentivos_V11.pdf</t>
   </si>
   <si>
     <t>04-01-PL-0001</t>
@@ -122,9 +122,6 @@
     <t>El Plan Institucional de Capacitación –PIC- está dirigido a todos los colaboradores de la Subred Integrada de Servicios de Salud Sur Occidente E.S.E e involucra en su aplicación, al personal en formación, docentes y personal tercerizado.
  En el cual se encuentra el Eje 4: Transformación Digital y Cibercultura: La transformación digital es el proceso por el cual las organizaciones, empresas y entidades reorganizan sus métodos de trabajo y estrategias en general para obtener más beneficios gracias a la digitalización de los procesos y a la implementación dinámica de las tecnologías de la información y la comunicación de manera articulada con y por el ser humano.
  A través del documento CONPES 397518, se adoptó la política nacional para la transformación digital e inteligencia artificial, con el fin de aumentar la generación de valor social y económico a través del uso estratégico de tecnologías digitales.</t>
-  </si>
-  <si>
-    <t>https://innovebogota.veeduriadistrital.gov.co:4282/app/api_preguntas/public/api/download-file-by-nombre/208/04-03-PL-0001_Plan_de_bienestar_social_e_incentivos_V11.pdf</t>
   </si>
   <si>
     <t>https://innovebogota.veeduriadistrital.gov.co:4282/app/api_preguntas/public/api/download-file-by-nombre/208/04-01-PL-0001_Plan_Institucional_de_capacitacion_V11 (1).pdf</t>
@@ -588,7 +585,7 @@
       <c r="D3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>29</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -636,7 +633,7 @@
       <c r="D4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>33</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -671,48 +668,7 @@
       </c>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K5" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O5" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="P5" s="4"/>
-    </row>
+    <row r="5" ht="14.25" customHeight="1"/>
     <row r="6" ht="14.25" customHeight="1"/>
     <row r="7" ht="14.25" customHeight="1"/>
     <row r="8" ht="14.25" customHeight="1"/>
@@ -1707,10 +1663,9 @@
     <row r="997" ht="14.25" customHeight="1"/>
     <row r="998" ht="14.25" customHeight="1"/>
     <row r="999" ht="14.25" customHeight="1"/>
-    <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="E4"/>
+    <hyperlink r:id="rId1" ref="E3"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
